--- a/data/Z1.xlsx
+++ b/data/Z1.xlsx
@@ -5,15 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProgram\HTML\实验提醒\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet name="实验安排" sheetId="1" r:id="rId1"/>
+    <sheet name="实验安排" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">实验安排!$A$1:$F$25</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="49">
   <si>
     <t>日期</t>
   </si>
@@ -50,6 +53,135 @@
   </si>
   <si>
     <t>实验地点</t>
+  </si>
+  <si>
+    <t>2026-10-12</t>
+  </si>
+  <si>
+    <t>第7周</t>
+  </si>
+  <si>
+    <t>星期一</t>
+  </si>
+  <si>
+    <t>第5-6节</t>
+  </si>
+  <si>
+    <t>电工电子实验</t>
+  </si>
+  <si>
+    <t>2026-10-19</t>
+  </si>
+  <si>
+    <t>第8周</t>
+  </si>
+  <si>
+    <t>209A</t>
+  </si>
+  <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
+    <t>星期三</t>
+  </si>
+  <si>
+    <t>第3-4节</t>
+  </si>
+  <si>
+    <t>机电实验</t>
+  </si>
+  <si>
+    <t>机械楼A502</t>
+  </si>
+  <si>
+    <t>机制实验</t>
+  </si>
+  <si>
+    <t>机械楼A106</t>
+  </si>
+  <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
+    <t>星期四</t>
+  </si>
+  <si>
+    <t>第1-2节</t>
+  </si>
+  <si>
+    <t>待定</t>
+  </si>
+  <si>
+    <t>2026-10-23</t>
+  </si>
+  <si>
+    <t>星期五</t>
+  </si>
+  <si>
+    <t>第7-8节</t>
+  </si>
+  <si>
+    <t>A108</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>第9周</t>
+  </si>
+  <si>
+    <t>2026-11-02</t>
+  </si>
+  <si>
+    <t>第10周</t>
+  </si>
+  <si>
+    <t>2026-11-04</t>
+  </si>
+  <si>
+    <t>机械楼A113</t>
+  </si>
+  <si>
+    <t>2026-11-09</t>
+  </si>
+  <si>
+    <t>第11周</t>
+  </si>
+  <si>
+    <t>2026-11-16</t>
+  </si>
+  <si>
+    <t>第12周</t>
+  </si>
+  <si>
+    <t>2026-11-18</t>
+  </si>
+  <si>
+    <t>A206</t>
+  </si>
+  <si>
+    <t>2026-11-23</t>
+  </si>
+  <si>
+    <t>第13周</t>
+  </si>
+  <si>
+    <t>智能传感实验</t>
+  </si>
+  <si>
+    <t>机械楼A302</t>
+  </si>
+  <si>
+    <t>2026-11-25</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
+    <t>第14周</t>
   </si>
 </sst>
 </file>
@@ -66,21 +198,20 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -88,7 +219,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -96,14 +227,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -111,7 +242,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -119,7 +250,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -127,7 +258,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -135,7 +266,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -143,14 +274,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -158,7 +289,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -166,7 +297,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -174,14 +305,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -189,42 +320,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -531,7 +662,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -678,10 +809,10 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -734,7 +865,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -754,44 +885,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -818,14 +949,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -852,6 +984,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -863,160 +996,131 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1027,8 +1131,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F1"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1038,7 +1144,7 @@
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" ht="14.5" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1058,7 +1164,506 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" ht="14.5" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" ht="14.5" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="14.5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" ht="14.5" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" ht="14.5" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" ht="14.5" spans="1:6">
+      <c r="A17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" ht="14.5" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" ht="14.5" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" ht="14.5" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" ht="14.5" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" ht="14.5" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" ht="14.5" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" ht="14.5" spans="1:6">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+    </row>
+    <row r="25" ht="14.5" spans="1:6">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" ht="14.5" spans="1:6">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" ht="14.5" spans="1:6">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" ht="14.5" spans="1:6">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="29" ht="14.5" spans="1:6">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+    </row>
+    <row r="30" ht="14.5" spans="1:6">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F25" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/data/Z1.xlsx
+++ b/data/Z1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProgram\HTML\实验提醒\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="55">
   <si>
     <t>日期</t>
   </si>
@@ -182,6 +182,98 @@
   </si>
   <si>
     <t>第14周</t>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>周</t>
+    </r>
+  </si>
+  <si>
+    <t>形势与政策</t>
+  </si>
+  <si>
+    <r>
+      <t>三山楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>106</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>周</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>三山楼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>102</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>周</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -194,7 +286,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,10 +302,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -663,156 +758,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1606,27 +1703,57 @@
     </row>
     <row r="24" ht="14.5" spans="1:6">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
+      <c r="B24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="25" ht="14.5" spans="1:6">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
+      <c r="B25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="26" ht="14.5" spans="1:6">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
+      <c r="B26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="27" ht="14.5" spans="1:6">
       <c r="A27" s="1"/>
